--- a/data/trans_orig/IP07C11-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C11-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35798</t>
+          <t>35354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44638</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63323</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77626</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21106</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32652</t>
+          <t>33059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20720</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>42930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>18525</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>31648</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42365</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19553</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>573</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>30067</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>41277</t>
+          <t>41451</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29241</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>40292</t>
+          <t>40148</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>62973</t>
+          <t>62935</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78692</t>
+          <t>78371</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35113</t>
+          <t>36034</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>32783</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>47135</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>32135</t>
+          <t>31886</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>44817</t>
+          <t>44682</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>68487</t>
+          <t>68261</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>87583</t>
+          <t>87652</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>36558</t>
+          <t>36172</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>35347</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>48524</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>67244</t>
+          <t>67810</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>163826</t>
+          <t>163944</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>190766</t>
+          <t>191355</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>187027</t>
+          <t>188840</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>213376</t>
+          <t>214901</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>362426</t>
+          <t>361287</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>399259</t>
+          <t>398761</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>85997</t>
+          <t>84056</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>111720</t>
+          <t>112731</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>83593</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>109153</t>
+          <t>107395</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>174038</t>
+          <t>174295</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>210663</t>
+          <t>211281</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>32575</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20928</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>47474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32584</t>
+          <t>32893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41618</t>
+          <t>40763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>49126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76844</t>
+          <t>76754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88840</t>
+          <t>88906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24004</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,47 +8485,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>62,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>22049</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18267</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25995</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>60,11%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>22049</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17633</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25600</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>72,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>58,02%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34284</t>
+          <t>34870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45315</t>
+          <t>45402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41566</t>
+          <t>41146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31756</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38728</t>
+          <t>38779</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30273</t>
+          <t>30167</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42095</t>
+          <t>42354</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23076</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>29001</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39596</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>29668</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>41241</t>
+          <t>40727</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>61382</t>
+          <t>61535</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77150</t>
+          <t>77061</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24193</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>39640</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>28067</t>
+          <t>28355</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>43230</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,47 +11895,47 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>54,27%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>35840</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>28431</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>42989</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
           <t>35,75%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>55,06%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>35840</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>29076</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>43410</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>81210</t>
+          <t>80990</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46529</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>44008</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>65552</t>
+          <t>66291</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>86535</t>
+          <t>86373</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>185963</t>
+          <t>184454</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>214592</t>
+          <t>212799</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>200874</t>
+          <t>201709</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>229545</t>
+          <t>228517</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>395745</t>
+          <t>396382</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>433429</t>
+          <t>434294</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>90141</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>116282</t>
+          <t>117949</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>85552</t>
+          <t>86717</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>112466</t>
+          <t>112985</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>184366</t>
+          <t>181294</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>222057</t>
+          <t>220176</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24872</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47724</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37864</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>47194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>53708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86291</t>
+          <t>87328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99734</t>
+          <t>99207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>27902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>41512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54523</t>
+          <t>54268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>803</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30443</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51106</t>
+          <t>51138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61604</t>
+          <t>61713</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20795</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>30737</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20441</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27877</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,7 +16925,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>46025</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55914</t>
+          <t>55484</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27754</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>25376</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>39086</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>57894</t>
+          <t>57748</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77046</t>
+          <t>77980</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31326</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>33701</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41988</t>
+          <t>41526</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>60615</t>
+          <t>61162</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>38246</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>25846</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t>39921</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>53731</t>
+          <t>53824</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>73887</t>
+          <t>74599</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>35617</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>49735</t>
+          <t>49962</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>33404</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>48065</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>73598</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>94455</t>
+          <t>92614</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>198021</t>
+          <t>199921</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>229982</t>
+          <t>231024</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>209830</t>
+          <t>209938</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>239751</t>
+          <t>241555</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>419028</t>
+          <t>417892</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>461240</t>
+          <t>460562</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>93947</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>94567</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>124017</t>
+          <t>124415</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>196382</t>
+          <t>197385</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>237216</t>
+          <t>238737</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
